--- a/output/pdf_financials_xlsx/ARGO.xlsx
+++ b/output/pdf_financials_xlsx/ARGO.xlsx
@@ -2203,16 +2203,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0.013388</v>
+        <v>0.035088</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.013388</v>
+        <v>0.212386</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.013388</v>
+        <v>0.209742</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0.013388</v>
+        <v>1.581909</v>
       </c>
     </row>
     <row r="93">
@@ -3718,7 +3718,11 @@
           <t>Share-based payment reserve 8</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -4670,7 +4674,11 @@
           <t>Share-based payment reserve 7</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E44" s="5" t="n">
         <v>0.0217</v>
       </c>

--- a/output/pdf_financials_xlsx/ARGO.xlsx
+++ b/output/pdf_financials_xlsx/ARGO.xlsx
@@ -1077,16 +1077,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.084047</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.098895</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.086352</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.29767</v>
       </c>
     </row>
     <row r="35">
@@ -1115,16 +1115,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.084047</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.098895</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.086352</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.29767</v>
       </c>
     </row>
     <row r="37">
@@ -1343,16 +1343,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.092198</v>
+        <v>0.008151</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.104249</v>
+        <v>0.005354</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.114485</v>
+        <v>0.028133</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.365273</v>
+        <v>0.067603</v>
       </c>
     </row>
     <row r="49">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">

--- a/output/pdf_financials_xlsx/ARGO.xlsx
+++ b/output/pdf_financials_xlsx/ARGO.xlsx
@@ -1712,16 +1712,16 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.030191</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.05189</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.048181</v>
       </c>
     </row>
     <row r="68">
